--- a/BeatnotePostHotCellF1=4/Jun25,2026/Fit_ResultJun25.xlsx
+++ b/BeatnotePostHotCellF1=4/Jun25,2026/Fit_ResultJun25.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Wolfwalker\Documents\git\6s7p\BeatnotePostHotCellF1=4\Jun25,2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Diego\git\6s7p\BeatnotePostHotCellF1=4\Jun25,2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DF09C5B-8516-41C8-8D57-922219C8CFA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60563D39-110A-4D86-B8F2-DFB0AFB79C92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38290" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="2" xr2:uid="{D9E101C5-8284-4B59-8B1C-2AD2D5F2FDD3}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{D9E101C5-8284-4B59-8B1C-2AD2D5F2FDD3}"/>
   </bookViews>
   <sheets>
     <sheet name="894" sheetId="2" r:id="rId1"/>
@@ -99,7 +99,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -471,9 +471,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{40C5617D-2BBC-4C21-ADC4-3687FEC8C6E3}">
   <dimension ref="A1:V33"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
-    <row r="1" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:22">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -508,7 +508,7 @@
       <c r="R1" s="1"/>
       <c r="S1" s="1"/>
     </row>
-    <row r="2" spans="1:22" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:22" ht="42.75">
       <c r="A2" s="1" t="s">
         <v>11</v>
       </c>
@@ -540,7 +540,7 @@
       <c r="R2" s="1"/>
       <c r="S2" s="1"/>
     </row>
-    <row r="3" spans="1:22" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:22" ht="42.75">
       <c r="A3" s="1" t="s">
         <v>12</v>
       </c>
@@ -574,7 +574,7 @@
       <c r="U3" s="1"/>
       <c r="V3" s="1"/>
     </row>
-    <row r="4" spans="1:22" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:22" ht="42.75">
       <c r="A4" s="1" t="s">
         <v>13</v>
       </c>
@@ -599,7 +599,7 @@
       <c r="H4" s="1"/>
       <c r="T4" s="1"/>
     </row>
-    <row r="5" spans="1:22" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:22" ht="42.75">
       <c r="A5" s="1" t="s">
         <v>14</v>
       </c>
@@ -624,7 +624,7 @@
       <c r="H5" s="1"/>
       <c r="T5" s="1"/>
     </row>
-    <row r="6" spans="1:22" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:22" ht="42.75">
       <c r="A6" s="1" t="s">
         <v>15</v>
       </c>
@@ -649,7 +649,7 @@
       <c r="H6" s="1"/>
       <c r="T6" s="1"/>
     </row>
-    <row r="7" spans="1:22" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:22" ht="42.75">
       <c r="A7" s="1" t="s">
         <v>16</v>
       </c>
@@ -674,7 +674,7 @@
       <c r="H7" s="1"/>
       <c r="S7" s="1"/>
     </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:22">
       <c r="A8" s="1"/>
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
@@ -685,7 +685,7 @@
       <c r="H8" s="1"/>
       <c r="S8" s="1"/>
     </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:22">
       <c r="A9" s="1"/>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
@@ -696,7 +696,7 @@
       <c r="H9" s="1"/>
       <c r="S9" s="1"/>
     </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:22">
       <c r="A10" s="1"/>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
@@ -707,7 +707,7 @@
       <c r="H10" s="1"/>
       <c r="S10" s="1"/>
     </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:22">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
@@ -718,7 +718,7 @@
       <c r="H11" s="1"/>
       <c r="R11" s="1"/>
     </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:22">
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
@@ -729,7 +729,7 @@
       <c r="H12" s="1"/>
       <c r="R12" s="1"/>
     </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:22">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
@@ -740,7 +740,7 @@
       <c r="H13" s="1"/>
       <c r="R13" s="1"/>
     </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:22">
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
@@ -751,7 +751,7 @@
       <c r="H14" s="1"/>
       <c r="R14" s="1"/>
     </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:22">
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
@@ -762,7 +762,7 @@
       <c r="H15" s="1"/>
       <c r="R15" s="1"/>
     </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:22">
       <c r="A16" s="1"/>
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
@@ -773,7 +773,7 @@
       <c r="H16" s="1"/>
       <c r="R16" s="1"/>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:8">
       <c r="A17" s="1"/>
       <c r="B17" s="1"/>
       <c r="C17" s="1"/>
@@ -783,7 +783,7 @@
       <c r="G17" s="1"/>
       <c r="H17" s="1"/>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:8">
       <c r="A18" s="1"/>
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
@@ -793,7 +793,7 @@
       <c r="G18" s="1"/>
       <c r="H18" s="1"/>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:8">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
@@ -803,7 +803,7 @@
       <c r="G19" s="1"/>
       <c r="H19" s="1"/>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:8">
       <c r="A20" s="1"/>
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
@@ -813,7 +813,7 @@
       <c r="G20" s="1"/>
       <c r="H20" s="1"/>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:8">
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
@@ -823,7 +823,7 @@
       <c r="G21" s="1"/>
       <c r="H21" s="1"/>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:8">
       <c r="A22" s="1"/>
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
@@ -832,7 +832,7 @@
       <c r="F22" s="1"/>
       <c r="G22" s="1"/>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:8">
       <c r="A23" s="1"/>
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
@@ -841,7 +841,7 @@
       <c r="F23" s="1"/>
       <c r="G23" s="1"/>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:8">
       <c r="A24" s="1"/>
       <c r="B24" s="1"/>
       <c r="C24" s="1"/>
@@ -850,7 +850,7 @@
       <c r="F24" s="1"/>
       <c r="G24" s="1"/>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:8">
       <c r="A25" s="1"/>
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
@@ -859,7 +859,7 @@
       <c r="F25" s="1"/>
       <c r="G25" s="1"/>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:8">
       <c r="A26" s="1"/>
       <c r="B26" s="1"/>
       <c r="C26" s="1"/>
@@ -868,7 +868,7 @@
       <c r="F26" s="1"/>
       <c r="G26" s="1"/>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:8">
       <c r="A27" s="1"/>
       <c r="B27" s="1"/>
       <c r="C27" s="1"/>
@@ -877,7 +877,7 @@
       <c r="F27" s="1"/>
       <c r="G27" s="1"/>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:8">
       <c r="A28" s="1"/>
       <c r="B28" s="1"/>
       <c r="C28" s="1"/>
@@ -886,7 +886,7 @@
       <c r="F28" s="1"/>
       <c r="G28" s="1"/>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:8">
       <c r="A29" s="1"/>
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
@@ -895,7 +895,7 @@
       <c r="F29" s="1"/>
       <c r="G29" s="1"/>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:8">
       <c r="A30" s="1"/>
       <c r="B30" s="1"/>
       <c r="C30" s="1"/>
@@ -904,7 +904,7 @@
       <c r="F30" s="1"/>
       <c r="G30" s="1"/>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:8">
       <c r="A31" s="1"/>
       <c r="B31" s="1"/>
       <c r="C31" s="1"/>
@@ -913,7 +913,7 @@
       <c r="F31" s="1"/>
       <c r="G31" s="1"/>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:8">
       <c r="A32" s="1"/>
       <c r="B32" s="1"/>
       <c r="C32" s="1"/>
@@ -922,7 +922,7 @@
       <c r="F32" s="1"/>
       <c r="G32" s="1"/>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:7">
       <c r="A33" s="1"/>
       <c r="B33" s="1"/>
       <c r="C33" s="1"/>
@@ -939,9 +939,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{011646E0-737D-49FA-A2CA-7848F848076B}">
   <dimension ref="A1:T40"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:20">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -977,7 +977,7 @@
       <c r="S1" s="1"/>
       <c r="T1" s="1"/>
     </row>
-    <row r="2" spans="1:20" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:20" ht="42.75">
       <c r="A2" s="1" t="s">
         <v>11</v>
       </c>
@@ -1004,7 +1004,7 @@
       </c>
       <c r="L2" s="1"/>
     </row>
-    <row r="3" spans="1:20" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:20" ht="42.75">
       <c r="A3" s="1" t="s">
         <v>12</v>
       </c>
@@ -1031,7 +1031,7 @@
       </c>
       <c r="L3" s="1"/>
     </row>
-    <row r="4" spans="1:20" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:20" ht="42.75">
       <c r="A4" s="1" t="s">
         <v>13</v>
       </c>
@@ -1057,7 +1057,7 @@
         <v>7.5216888981779703E-4</v>
       </c>
     </row>
-    <row r="5" spans="1:20" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:20" ht="42.75">
       <c r="A5" s="1" t="s">
         <v>17</v>
       </c>
@@ -1083,7 +1083,7 @@
         <v>7.9987941790931596E-4</v>
       </c>
     </row>
-    <row r="6" spans="1:20" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:20" ht="42.75">
       <c r="A6" s="1" t="s">
         <v>14</v>
       </c>
@@ -1109,7 +1109,7 @@
         <v>1.15715386763279E-3</v>
       </c>
     </row>
-    <row r="7" spans="1:20" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:20" ht="42.75">
       <c r="A7" s="1" t="s">
         <v>15</v>
       </c>
@@ -1135,7 +1135,7 @@
         <v>5.8653519092990796E-4</v>
       </c>
     </row>
-    <row r="8" spans="1:20" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:20" ht="42.75">
       <c r="A8" s="1" t="s">
         <v>16</v>
       </c>
@@ -1161,7 +1161,7 @@
         <v>1.03436630399861E-3</v>
       </c>
     </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:20">
       <c r="A10" s="1"/>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
@@ -1171,7 +1171,7 @@
       <c r="G10" s="1"/>
       <c r="H10" s="1"/>
     </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:20">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
@@ -1181,7 +1181,7 @@
       <c r="G11" s="1"/>
       <c r="H11" s="1"/>
     </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:20">
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
@@ -1191,7 +1191,7 @@
       <c r="G12" s="1"/>
       <c r="H12" s="1"/>
     </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:20">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
@@ -1201,7 +1201,7 @@
       <c r="G13" s="1"/>
       <c r="H13" s="1"/>
     </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:20">
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
@@ -1211,7 +1211,7 @@
       <c r="G14" s="1"/>
       <c r="H14" s="1"/>
     </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:20">
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
@@ -1221,7 +1221,7 @@
       <c r="G15" s="1"/>
       <c r="H15" s="1"/>
     </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:20">
       <c r="A16" s="1"/>
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
@@ -1231,7 +1231,7 @@
       <c r="G16" s="1"/>
       <c r="H16" s="1"/>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:8">
       <c r="A17" s="1"/>
       <c r="B17" s="1"/>
       <c r="C17" s="1"/>
@@ -1241,7 +1241,7 @@
       <c r="G17" s="1"/>
       <c r="H17" s="1"/>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:8">
       <c r="A18" s="1"/>
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
@@ -1251,7 +1251,7 @@
       <c r="G18" s="1"/>
       <c r="H18" s="1"/>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:8">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
@@ -1261,7 +1261,7 @@
       <c r="G19" s="1"/>
       <c r="H19" s="1"/>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:8">
       <c r="A20" s="1"/>
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
@@ -1271,7 +1271,7 @@
       <c r="G20" s="1"/>
       <c r="H20" s="1"/>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:8">
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
@@ -1281,7 +1281,7 @@
       <c r="G21" s="1"/>
       <c r="H21" s="1"/>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:8">
       <c r="A22" s="1"/>
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
@@ -1291,7 +1291,7 @@
       <c r="G22" s="1"/>
       <c r="H22" s="1"/>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:8">
       <c r="A23" s="1"/>
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
@@ -1301,7 +1301,7 @@
       <c r="G23" s="1"/>
       <c r="H23" s="1"/>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:8">
       <c r="A24" s="1"/>
       <c r="B24" s="1"/>
       <c r="C24" s="1"/>
@@ -1311,7 +1311,7 @@
       <c r="G24" s="1"/>
       <c r="H24" s="1"/>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:8">
       <c r="A25" s="1"/>
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
@@ -1321,7 +1321,7 @@
       <c r="G25" s="1"/>
       <c r="H25" s="1"/>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:8">
       <c r="A26" s="1"/>
       <c r="B26" s="1"/>
       <c r="C26" s="1"/>
@@ -1331,7 +1331,7 @@
       <c r="G26" s="1"/>
       <c r="H26" s="1"/>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:8">
       <c r="A27" s="1"/>
       <c r="B27" s="1"/>
       <c r="C27" s="1"/>
@@ -1341,7 +1341,7 @@
       <c r="G27" s="1"/>
       <c r="H27" s="1"/>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:8">
       <c r="A28" s="1"/>
       <c r="B28" s="1"/>
       <c r="C28" s="1"/>
@@ -1351,7 +1351,7 @@
       <c r="G28" s="1"/>
       <c r="H28" s="1"/>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:8">
       <c r="A29" s="1"/>
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
@@ -1361,7 +1361,7 @@
       <c r="G29" s="1"/>
       <c r="H29" s="1"/>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:8">
       <c r="A30" s="1"/>
       <c r="B30" s="1"/>
       <c r="C30" s="1"/>
@@ -1371,7 +1371,7 @@
       <c r="G30" s="1"/>
       <c r="H30" s="1"/>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:8">
       <c r="A31" s="1"/>
       <c r="B31" s="1"/>
       <c r="C31" s="1"/>
@@ -1381,7 +1381,7 @@
       <c r="G31" s="1"/>
       <c r="H31" s="1"/>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:8">
       <c r="A32" s="1"/>
       <c r="B32" s="1"/>
       <c r="C32" s="1"/>
@@ -1391,7 +1391,7 @@
       <c r="G32" s="1"/>
       <c r="H32" s="1"/>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:8">
       <c r="A33" s="1"/>
       <c r="B33" s="1"/>
       <c r="C33" s="1"/>
@@ -1401,7 +1401,7 @@
       <c r="G33" s="1"/>
       <c r="H33" s="1"/>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:8">
       <c r="A34" s="1"/>
       <c r="B34" s="1"/>
       <c r="C34" s="1"/>
@@ -1411,7 +1411,7 @@
       <c r="G34" s="1"/>
       <c r="H34" s="1"/>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:8">
       <c r="A35" s="1"/>
       <c r="B35" s="1"/>
       <c r="C35" s="1"/>
@@ -1421,7 +1421,7 @@
       <c r="G35" s="1"/>
       <c r="H35" s="1"/>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:8">
       <c r="A36" s="1"/>
       <c r="B36" s="1"/>
       <c r="C36" s="1"/>
@@ -1431,7 +1431,7 @@
       <c r="G36" s="1"/>
       <c r="H36" s="1"/>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:8">
       <c r="A37" s="1"/>
       <c r="B37" s="1"/>
       <c r="C37" s="1"/>
@@ -1441,7 +1441,7 @@
       <c r="G37" s="1"/>
       <c r="H37" s="1"/>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:8">
       <c r="A38" s="1"/>
       <c r="B38" s="1"/>
       <c r="C38" s="1"/>
@@ -1451,7 +1451,7 @@
       <c r="G38" s="1"/>
       <c r="H38" s="1"/>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:8">
       <c r="A39" s="1"/>
       <c r="B39" s="1"/>
       <c r="C39" s="1"/>
@@ -1461,7 +1461,7 @@
       <c r="G39" s="1"/>
       <c r="H39" s="1"/>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:8">
       <c r="A40" s="1"/>
       <c r="B40" s="1"/>
       <c r="C40" s="1"/>
@@ -1479,12 +1479,12 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CF8CB368-1F4F-4C65-B86B-93EC676CB77B}">
   <dimension ref="A1:F39"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="4" max="4" width="16.7265625" customWidth="1"/>
+    <col min="4" max="4" width="16.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1495,7 +1495,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:6" ht="42.75">
       <c r="A2" s="1" t="s">
         <v>11</v>
       </c>
@@ -1512,7 +1512,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:6" ht="42.75">
       <c r="A3" s="1" t="s">
         <v>12</v>
       </c>
@@ -1534,7 +1534,7 @@
         <v>0.17332711803922066</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:6" ht="42.75">
       <c r="A4" s="1" t="s">
         <v>13</v>
       </c>
@@ -1556,7 +1556,7 @@
         <v>2.1779949830740579E-3</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:6" ht="42.75">
       <c r="A5" s="1" t="s">
         <v>14</v>
       </c>
@@ -1578,7 +1578,7 @@
         <v>5.1299689196796878E-3</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:6" ht="42.75">
       <c r="A6" s="1" t="s">
         <v>15</v>
       </c>
@@ -1589,7 +1589,7 @@
         <v>0.16979104098602099</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:6" ht="42.75">
       <c r="A7" s="1" t="s">
         <v>16</v>
       </c>
@@ -1600,151 +1600,151 @@
         <v>0.175682517244173</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:6">
       <c r="A8" s="1"/>
       <c r="B8" s="1"/>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:6">
       <c r="A9" s="1"/>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:6">
       <c r="A10" s="1"/>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:6">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:6">
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:6">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:6">
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:6">
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:6">
       <c r="A16" s="1"/>
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:3">
       <c r="A17" s="1"/>
       <c r="B17" s="1"/>
       <c r="C17" s="1"/>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:3">
       <c r="A18" s="1"/>
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:3">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:3">
       <c r="A20" s="1"/>
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:3">
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:3">
       <c r="A22" s="1"/>
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:3">
       <c r="A23" s="1"/>
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:3">
       <c r="A24" s="1"/>
       <c r="B24" s="1"/>
       <c r="C24" s="1"/>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:3">
       <c r="A25" s="1"/>
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:3">
       <c r="A26" s="1"/>
       <c r="B26" s="1"/>
       <c r="C26" s="1"/>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:3">
       <c r="A27" s="1"/>
       <c r="B27" s="1"/>
       <c r="C27" s="1"/>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:3">
       <c r="A28" s="1"/>
       <c r="B28" s="1"/>
       <c r="C28" s="1"/>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:3">
       <c r="A29" s="1"/>
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:3">
       <c r="A30" s="1"/>
       <c r="B30" s="1"/>
       <c r="C30" s="1"/>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:3">
       <c r="A31" s="1"/>
       <c r="B31" s="1"/>
       <c r="C31" s="1"/>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:3">
       <c r="A32" s="1"/>
       <c r="B32" s="1"/>
       <c r="C32" s="1"/>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:3">
       <c r="A33" s="1"/>
       <c r="B33" s="1"/>
       <c r="C33" s="1"/>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:3">
       <c r="C34" s="1"/>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:3">
       <c r="C35" s="1"/>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:3">
       <c r="C36" s="1"/>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:3">
       <c r="C37" s="1"/>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:3">
       <c r="C38" s="1"/>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:3">
       <c r="C39" s="1"/>
     </row>
   </sheetData>
